--- a/final_data_pipeline/output/311611_elec_options.xlsx
+++ b/final_data_pipeline/output/311611_elec_options.xlsx
@@ -996,7 +996,7 @@
         <v>44138.20517500199</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE2">
         <v>8000</v>
@@ -1091,7 +1091,7 @@
         <v>139</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE3">
         <v>8000</v>
@@ -1186,7 +1186,7 @@
         <v>139</v>
       </c>
       <c r="AD4">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE4">
         <v>8000</v>
@@ -1281,7 +1281,7 @@
         <v>139</v>
       </c>
       <c r="AD5">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE5">
         <v>8000</v>
@@ -1376,7 +1376,7 @@
         <v>139</v>
       </c>
       <c r="AD6">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE6">
         <v>8000</v>
@@ -1471,7 +1471,7 @@
         <v>139</v>
       </c>
       <c r="AD7">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE7">
         <v>8000</v>
@@ -1566,7 +1566,7 @@
         <v>139</v>
       </c>
       <c r="AD8">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE8">
         <v>8000</v>
@@ -1661,7 +1661,7 @@
         <v>139</v>
       </c>
       <c r="AD9">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE9">
         <v>8000</v>
@@ -1756,7 +1756,7 @@
         <v>139</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE10">
         <v>8000</v>
@@ -1851,7 +1851,7 @@
         <v>139</v>
       </c>
       <c r="AD11">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE11">
         <v>8000</v>
@@ -1949,7 +1949,7 @@
         <v>139</v>
       </c>
       <c r="AD12">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE12">
         <v>8000</v>
@@ -2047,7 +2047,7 @@
         <v>139</v>
       </c>
       <c r="AD13">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE13">
         <v>8000</v>
@@ -2142,7 +2142,7 @@
         <v>139</v>
       </c>
       <c r="AD14">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE14">
         <v>8000</v>
@@ -2237,7 +2237,7 @@
         <v>139</v>
       </c>
       <c r="AD15">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE15">
         <v>8000</v>
@@ -2332,7 +2332,7 @@
         <v>139</v>
       </c>
       <c r="AD16">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE16">
         <v>8000</v>
@@ -6435,7 +6435,7 @@
         <v>139</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6530,7 +6530,7 @@
         <v>139</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6625,7 +6625,7 @@
         <v>139</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -6720,7 +6720,7 @@
         <v>139</v>
       </c>
       <c r="AD62">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE62">
         <v>8000</v>
@@ -6818,7 +6818,7 @@
         <v>139</v>
       </c>
       <c r="AD63">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE63">
         <v>8000</v>
@@ -6913,7 +6913,7 @@
         <v>139</v>
       </c>
       <c r="AD64">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE64">
         <v>8000</v>
@@ -7008,7 +7008,7 @@
         <v>139</v>
       </c>
       <c r="AD65">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE65">
         <v>8000</v>
@@ -7103,7 +7103,7 @@
         <v>139</v>
       </c>
       <c r="AD66">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE66">
         <v>8000</v>
@@ -7198,7 +7198,7 @@
         <v>139</v>
       </c>
       <c r="AD67">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE67">
         <v>8000</v>
@@ -7293,7 +7293,7 @@
         <v>139</v>
       </c>
       <c r="AD68">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE68">
         <v>8000</v>
@@ -7388,7 +7388,7 @@
         <v>139</v>
       </c>
       <c r="AD69">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE69">
         <v>8000</v>
@@ -7483,7 +7483,7 @@
         <v>139</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7578,7 +7578,7 @@
         <v>139</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -7676,7 +7676,7 @@
         <v>139</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>-0.763888888888889</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -12652,7 +12652,7 @@
         <v>139</v>
       </c>
       <c r="AD124">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE124">
         <v>8000</v>
@@ -12747,7 +12747,7 @@
         <v>139</v>
       </c>
       <c r="AD125">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE125">
         <v>8000</v>
@@ -12842,7 +12842,7 @@
         <v>139</v>
       </c>
       <c r="AD126">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE126">
         <v>8000</v>
@@ -12937,7 +12937,7 @@
         <v>139</v>
       </c>
       <c r="AD127">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE127">
         <v>8000</v>
@@ -13032,7 +13032,7 @@
         <v>139</v>
       </c>
       <c r="AD128">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE128">
         <v>8000</v>
@@ -13127,7 +13127,7 @@
         <v>139</v>
       </c>
       <c r="AD129">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE129">
         <v>8000</v>
@@ -13222,7 +13222,7 @@
         <v>139</v>
       </c>
       <c r="AD130">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE130">
         <v>8000</v>
@@ -13317,7 +13317,7 @@
         <v>139</v>
       </c>
       <c r="AD131">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE131">
         <v>8000</v>
@@ -13412,7 +13412,7 @@
         <v>139</v>
       </c>
       <c r="AD132">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE132">
         <v>8000</v>
@@ -13507,7 +13507,7 @@
         <v>139</v>
       </c>
       <c r="AD133">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE133">
         <v>8000</v>
@@ -13605,7 +13605,7 @@
         <v>139</v>
       </c>
       <c r="AD134">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE134">
         <v>8000</v>
@@ -13700,7 +13700,7 @@
         <v>139</v>
       </c>
       <c r="AD135">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE135">
         <v>8000</v>
@@ -13795,7 +13795,7 @@
         <v>139</v>
       </c>
       <c r="AD136">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE136">
         <v>8000</v>
@@ -13890,7 +13890,7 @@
         <v>139</v>
       </c>
       <c r="AD137">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE137">
         <v>8000</v>
@@ -15992,7 +15992,7 @@
         <v>139</v>
       </c>
       <c r="AD159">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE159">
         <v>8000</v>
@@ -16087,7 +16087,7 @@
         <v>139</v>
       </c>
       <c r="AD160">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE160">
         <v>8000</v>
@@ -16182,7 +16182,7 @@
         <v>139</v>
       </c>
       <c r="AD161">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE161">
         <v>8000</v>
@@ -16277,7 +16277,7 @@
         <v>139</v>
       </c>
       <c r="AD162">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE162">
         <v>8000</v>
@@ -16372,7 +16372,7 @@
         <v>139</v>
       </c>
       <c r="AD163">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE163">
         <v>8000</v>
@@ -16467,7 +16467,7 @@
         <v>139</v>
       </c>
       <c r="AD164">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE164">
         <v>8000</v>
@@ -16562,7 +16562,7 @@
         <v>139</v>
       </c>
       <c r="AD165">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE165">
         <v>8000</v>
@@ -17996,7 +17996,7 @@
         <v>139</v>
       </c>
       <c r="AD180">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE180">
         <v>8000</v>
@@ -18094,7 +18094,7 @@
         <v>139</v>
       </c>
       <c r="AD181">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE181">
         <v>8000</v>
@@ -18189,7 +18189,7 @@
         <v>139</v>
       </c>
       <c r="AD182">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE182">
         <v>8000</v>
@@ -18284,7 +18284,7 @@
         <v>139</v>
       </c>
       <c r="AD183">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE183">
         <v>8000</v>
@@ -18379,7 +18379,7 @@
         <v>139</v>
       </c>
       <c r="AD184">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE184">
         <v>8000</v>
@@ -18474,7 +18474,7 @@
         <v>139</v>
       </c>
       <c r="AD185">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE185">
         <v>8000</v>
@@ -18569,7 +18569,7 @@
         <v>139</v>
       </c>
       <c r="AD186">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE186">
         <v>8000</v>
@@ -18664,7 +18664,7 @@
         <v>139</v>
       </c>
       <c r="AD187">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE187">
         <v>8000</v>
@@ -18759,7 +18759,7 @@
         <v>139</v>
       </c>
       <c r="AD188">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE188">
         <v>8000</v>
@@ -18854,7 +18854,7 @@
         <v>139</v>
       </c>
       <c r="AD189">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE189">
         <v>8000</v>
@@ -18949,7 +18949,7 @@
         <v>139</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -19044,7 +19044,7 @@
         <v>139</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -19139,7 +19139,7 @@
         <v>139</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -19234,7 +19234,7 @@
         <v>139</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -20665,7 +20665,7 @@
         <v>139</v>
       </c>
       <c r="AD208">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE208">
         <v>8000</v>
@@ -20760,7 +20760,7 @@
         <v>139</v>
       </c>
       <c r="AD209">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE209">
         <v>8000</v>
@@ -20855,7 +20855,7 @@
         <v>139</v>
       </c>
       <c r="AD210">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE210">
         <v>8000</v>
@@ -20950,7 +20950,7 @@
         <v>139</v>
       </c>
       <c r="AD211">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE211">
         <v>8000</v>
@@ -21045,7 +21045,7 @@
         <v>139</v>
       </c>
       <c r="AD212">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE212">
         <v>8000</v>
@@ -21143,7 +21143,7 @@
         <v>139</v>
       </c>
       <c r="AD213">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE213">
         <v>8000</v>
@@ -21241,7 +21241,7 @@
         <v>139</v>
       </c>
       <c r="AD214">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE214">
         <v>8000</v>
@@ -21336,7 +21336,7 @@
         <v>139</v>
       </c>
       <c r="AD215">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE215">
         <v>8000</v>
@@ -21431,7 +21431,7 @@
         <v>139</v>
       </c>
       <c r="AD216">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE216">
         <v>8000</v>
@@ -21526,7 +21526,7 @@
         <v>139</v>
       </c>
       <c r="AD217">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE217">
         <v>8000</v>
@@ -21621,7 +21621,7 @@
         <v>139</v>
       </c>
       <c r="AD218">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE218">
         <v>8000</v>
@@ -21716,7 +21716,7 @@
         <v>139</v>
       </c>
       <c r="AD219">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE219">
         <v>8000</v>
@@ -21811,7 +21811,7 @@
         <v>139</v>
       </c>
       <c r="AD220">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE220">
         <v>8000</v>
@@ -21906,7 +21906,7 @@
         <v>139</v>
       </c>
       <c r="AD221">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE221">
         <v>8000</v>
@@ -23328,7 +23328,7 @@
         <v>31090.90891717494</v>
       </c>
       <c r="AD236">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE236">
         <v>8000</v>
@@ -23423,7 +23423,7 @@
         <v>139</v>
       </c>
       <c r="AD237">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE237">
         <v>8000</v>
@@ -23518,7 +23518,7 @@
         <v>139</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE238">
         <v>8000</v>
@@ -23613,7 +23613,7 @@
         <v>139</v>
       </c>
       <c r="AD239">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE239">
         <v>8000</v>
@@ -23708,7 +23708,7 @@
         <v>139</v>
       </c>
       <c r="AD240">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE240">
         <v>8000</v>
@@ -23803,7 +23803,7 @@
         <v>139</v>
       </c>
       <c r="AD241">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE241">
         <v>8000</v>
@@ -23898,7 +23898,7 @@
         <v>139</v>
       </c>
       <c r="AD242">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE242">
         <v>8000</v>
@@ -23996,7 +23996,7 @@
         <v>139</v>
       </c>
       <c r="AD243">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE243">
         <v>8000</v>
@@ -24094,7 +24094,7 @@
         <v>139</v>
       </c>
       <c r="AD244">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE244">
         <v>8000</v>
@@ -24189,7 +24189,7 @@
         <v>139</v>
       </c>
       <c r="AD245">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE245">
         <v>8000</v>
@@ -24284,7 +24284,7 @@
         <v>139</v>
       </c>
       <c r="AD246">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE246">
         <v>8000</v>
@@ -24379,7 +24379,7 @@
         <v>139</v>
       </c>
       <c r="AD247">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE247">
         <v>8000</v>
@@ -24474,7 +24474,7 @@
         <v>139</v>
       </c>
       <c r="AD248">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE248">
         <v>8000</v>
@@ -24569,7 +24569,7 @@
         <v>139</v>
       </c>
       <c r="AD249">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE249">
         <v>8000</v>
@@ -24664,7 +24664,7 @@
         <v>139</v>
       </c>
       <c r="AD250">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE250">
         <v>8000</v>
@@ -26095,7 +26095,7 @@
         <v>139</v>
       </c>
       <c r="AD265">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE265">
         <v>8000</v>
@@ -26190,7 +26190,7 @@
         <v>139</v>
       </c>
       <c r="AD266">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE266">
         <v>8000</v>
@@ -26285,7 +26285,7 @@
         <v>139</v>
       </c>
       <c r="AD267">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE267">
         <v>8000</v>
@@ -26383,7 +26383,7 @@
         <v>139</v>
       </c>
       <c r="AD268">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE268">
         <v>8000</v>
@@ -26478,7 +26478,7 @@
         <v>139</v>
       </c>
       <c r="AD269">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE269">
         <v>8000</v>
@@ -26573,7 +26573,7 @@
         <v>139</v>
       </c>
       <c r="AD270">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE270">
         <v>8000</v>
@@ -26668,7 +26668,7 @@
         <v>139</v>
       </c>
       <c r="AD271">
-        <v>10</v>
+        <v>12.66820987654322</v>
       </c>
       <c r="AE271">
         <v>8000</v>
@@ -27431,7 +27431,7 @@
         <v>139</v>
       </c>
       <c r="AD279">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE279">
         <v>8000</v>
@@ -27526,7 +27526,7 @@
         <v>139</v>
       </c>
       <c r="AD280">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE280">
         <v>8000</v>
@@ -27621,7 +27621,7 @@
         <v>139</v>
       </c>
       <c r="AD281">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE281">
         <v>8000</v>
@@ -27716,7 +27716,7 @@
         <v>139</v>
       </c>
       <c r="AD282">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE282">
         <v>8000</v>
@@ -27811,7 +27811,7 @@
         <v>139</v>
       </c>
       <c r="AD283">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE283">
         <v>8000</v>
@@ -27909,7 +27909,7 @@
         <v>139</v>
       </c>
       <c r="AD284">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE284">
         <v>8000</v>
@@ -28004,7 +28004,7 @@
         <v>139</v>
       </c>
       <c r="AD285">
-        <v>10</v>
+        <v>5.462962962962945</v>
       </c>
       <c r="AE285">
         <v>8000</v>
@@ -28099,7 +28099,7 @@
         <v>139</v>
       </c>
       <c r="AD286">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE286">
         <v>8000</v>
@@ -28194,7 +28194,7 @@
         <v>139</v>
       </c>
       <c r="AD287">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE287">
         <v>8000</v>
@@ -28289,7 +28289,7 @@
         <v>139</v>
       </c>
       <c r="AD288">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE288">
         <v>8000</v>
@@ -28384,7 +28384,7 @@
         <v>139</v>
       </c>
       <c r="AD289">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE289">
         <v>8000</v>
@@ -28479,7 +28479,7 @@
         <v>139</v>
       </c>
       <c r="AD290">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE290">
         <v>8000</v>
@@ -28574,7 +28574,7 @@
         <v>139</v>
       </c>
       <c r="AD291">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE291">
         <v>8000</v>
@@ -28669,7 +28669,7 @@
         <v>139</v>
       </c>
       <c r="AD292">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE292">
         <v>8000</v>
@@ -28764,7 +28764,7 @@
         <v>139</v>
       </c>
       <c r="AD293">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE293">
         <v>8000</v>
@@ -28859,7 +28859,7 @@
         <v>139</v>
       </c>
       <c r="AD294">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE294">
         <v>8000</v>
@@ -28954,7 +28954,7 @@
         <v>139</v>
       </c>
       <c r="AD295">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE295">
         <v>8000</v>
@@ -29049,7 +29049,7 @@
         <v>139</v>
       </c>
       <c r="AD296">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE296">
         <v>8000</v>
@@ -29144,7 +29144,7 @@
         <v>139</v>
       </c>
       <c r="AD297">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE297">
         <v>8000</v>
@@ -29242,7 +29242,7 @@
         <v>139</v>
       </c>
       <c r="AD298">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE298">
         <v>8000</v>
@@ -29340,7 +29340,7 @@
         <v>139</v>
       </c>
       <c r="AD299">
-        <v>10</v>
+        <v>19.60879629629628</v>
       </c>
       <c r="AE299">
         <v>8000</v>
@@ -29438,7 +29438,7 @@
         <v>139</v>
       </c>
       <c r="AD300">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE300">
         <v>8000</v>
@@ -29536,7 +29536,7 @@
         <v>139</v>
       </c>
       <c r="AD301">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE301">
         <v>8000</v>
@@ -29631,7 +29631,7 @@
         <v>139</v>
       </c>
       <c r="AD302">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE302">
         <v>8000</v>
@@ -29726,7 +29726,7 @@
         <v>139</v>
       </c>
       <c r="AD303">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE303">
         <v>8000</v>
@@ -29821,7 +29821,7 @@
         <v>139</v>
       </c>
       <c r="AD304">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE304">
         <v>8000</v>
@@ -29916,7 +29916,7 @@
         <v>139</v>
       </c>
       <c r="AD305">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE305">
         <v>8000</v>
@@ -30011,7 +30011,7 @@
         <v>139</v>
       </c>
       <c r="AD306">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE306">
         <v>8000</v>
@@ -30106,7 +30106,7 @@
         <v>139</v>
       </c>
       <c r="AD307">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE307">
         <v>8000</v>
@@ -30204,7 +30204,7 @@
         <v>139</v>
       </c>
       <c r="AD308">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE308">
         <v>8000</v>
@@ -30299,7 +30299,7 @@
         <v>139</v>
       </c>
       <c r="AD309">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE309">
         <v>8000</v>
@@ -30394,7 +30394,7 @@
         <v>139</v>
       </c>
       <c r="AD310">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE310">
         <v>8000</v>
@@ -30489,7 +30489,7 @@
         <v>139</v>
       </c>
       <c r="AD311">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE311">
         <v>8000</v>
@@ -30584,7 +30584,7 @@
         <v>139</v>
       </c>
       <c r="AD312">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE312">
         <v>8000</v>
@@ -30679,7 +30679,7 @@
         <v>139</v>
       </c>
       <c r="AD313">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE313">
         <v>8000</v>
@@ -30774,7 +30774,7 @@
         <v>139</v>
       </c>
       <c r="AD314">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE314">
         <v>8000</v>
@@ -30869,7 +30869,7 @@
         <v>139</v>
       </c>
       <c r="AD315">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE315">
         <v>8000</v>
@@ -30964,7 +30964,7 @@
         <v>139</v>
       </c>
       <c r="AD316">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE316">
         <v>8000</v>
@@ -31059,7 +31059,7 @@
         <v>139</v>
       </c>
       <c r="AD317">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE317">
         <v>8000</v>
@@ -31154,7 +31154,7 @@
         <v>139</v>
       </c>
       <c r="AD318">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE318">
         <v>8000</v>
@@ -31249,7 +31249,7 @@
         <v>139</v>
       </c>
       <c r="AD319">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE319">
         <v>8000</v>
@@ -31344,7 +31344,7 @@
         <v>139</v>
       </c>
       <c r="AD320">
-        <v>10</v>
+        <v>14.96875</v>
       </c>
       <c r="AE320">
         <v>8000</v>
@@ -31442,7 +31442,7 @@
         <v>139</v>
       </c>
       <c r="AD321">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE321">
         <v>8000</v>
@@ -31537,7 +31537,7 @@
         <v>139</v>
       </c>
       <c r="AD322">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE322">
         <v>8000</v>
@@ -31632,7 +31632,7 @@
         <v>139</v>
       </c>
       <c r="AD323">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE323">
         <v>8000</v>
@@ -31727,7 +31727,7 @@
         <v>139</v>
       </c>
       <c r="AD324">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE324">
         <v>8000</v>
@@ -31822,7 +31822,7 @@
         <v>139</v>
       </c>
       <c r="AD325">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE325">
         <v>8000</v>
@@ -31917,7 +31917,7 @@
         <v>139</v>
       </c>
       <c r="AD326">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE326">
         <v>8000</v>
@@ -32015,7 +32015,7 @@
         <v>139</v>
       </c>
       <c r="AD327">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE327">
         <v>8000</v>
@@ -32110,7 +32110,7 @@
         <v>139</v>
       </c>
       <c r="AD328">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE328">
         <v>8000</v>
@@ -32205,7 +32205,7 @@
         <v>139</v>
       </c>
       <c r="AD329">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE329">
         <v>8000</v>
@@ -32300,7 +32300,7 @@
         <v>139</v>
       </c>
       <c r="AD330">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE330">
         <v>8000</v>
@@ -32395,7 +32395,7 @@
         <v>139</v>
       </c>
       <c r="AD331">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE331">
         <v>8000</v>
@@ -32490,7 +32490,7 @@
         <v>139</v>
       </c>
       <c r="AD332">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE332">
         <v>8000</v>
@@ -32585,7 +32585,7 @@
         <v>139</v>
       </c>
       <c r="AD333">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE333">
         <v>8000</v>
@@ -32680,7 +32680,7 @@
         <v>139</v>
       </c>
       <c r="AD334">
-        <v>10</v>
+        <v>15.36574074074072</v>
       </c>
       <c r="AE334">
         <v>8000</v>
@@ -32775,7 +32775,7 @@
         <v>139</v>
       </c>
       <c r="AD335">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE335">
         <v>8000</v>
@@ -32873,7 +32873,7 @@
         <v>139</v>
       </c>
       <c r="AD336">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE336">
         <v>8000</v>
@@ -32968,7 +32968,7 @@
         <v>139</v>
       </c>
       <c r="AD337">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE337">
         <v>8000</v>
@@ -33063,7 +33063,7 @@
         <v>139</v>
       </c>
       <c r="AD338">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE338">
         <v>8000</v>
@@ -33161,7 +33161,7 @@
         <v>139</v>
       </c>
       <c r="AD339">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE339">
         <v>8000</v>
@@ -33256,7 +33256,7 @@
         <v>139</v>
       </c>
       <c r="AD340">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE340">
         <v>8000</v>
@@ -33351,7 +33351,7 @@
         <v>139</v>
       </c>
       <c r="AD341">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE341">
         <v>8000</v>
@@ -33446,7 +33446,7 @@
         <v>139</v>
       </c>
       <c r="AD342">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE342">
         <v>8000</v>
@@ -33541,7 +33541,7 @@
         <v>139</v>
       </c>
       <c r="AD343">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE343">
         <v>8000</v>
@@ -33636,7 +33636,7 @@
         <v>139</v>
       </c>
       <c r="AD344">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE344">
         <v>8000</v>
@@ -33731,7 +33731,7 @@
         <v>139</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE345">
         <v>8000</v>
@@ -33826,7 +33826,7 @@
         <v>139</v>
       </c>
       <c r="AD346">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE346">
         <v>8000</v>
@@ -33921,7 +33921,7 @@
         <v>139</v>
       </c>
       <c r="AD347">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE347">
         <v>8000</v>
@@ -34016,7 +34016,7 @@
         <v>139</v>
       </c>
       <c r="AD348">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE348">
         <v>8000</v>
@@ -40209,7 +40209,7 @@
         <v>139</v>
       </c>
       <c r="AD413">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE413">
         <v>8000</v>
@@ -40304,7 +40304,7 @@
         <v>139</v>
       </c>
       <c r="AD414">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE414">
         <v>8000</v>
@@ -40402,7 +40402,7 @@
         <v>139</v>
       </c>
       <c r="AD415">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE415">
         <v>8000</v>
@@ -40500,7 +40500,7 @@
         <v>139</v>
       </c>
       <c r="AD416">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE416">
         <v>8000</v>
@@ -40595,7 +40595,7 @@
         <v>139</v>
       </c>
       <c r="AD417">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE417">
         <v>8000</v>
@@ -40690,7 +40690,7 @@
         <v>139</v>
       </c>
       <c r="AD418">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE418">
         <v>8000</v>
@@ -40785,7 +40785,7 @@
         <v>139</v>
       </c>
       <c r="AD419">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE419">
         <v>8000</v>
@@ -40880,7 +40880,7 @@
         <v>139</v>
       </c>
       <c r="AD420">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE420">
         <v>8000</v>
@@ -40975,7 +40975,7 @@
         <v>139</v>
       </c>
       <c r="AD421">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE421">
         <v>8000</v>
@@ -41070,7 +41070,7 @@
         <v>139</v>
       </c>
       <c r="AD422">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE422">
         <v>8000</v>
@@ -41165,7 +41165,7 @@
         <v>139</v>
       </c>
       <c r="AD423">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE423">
         <v>8000</v>
@@ -41260,7 +41260,7 @@
         <v>139</v>
       </c>
       <c r="AD424">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE424">
         <v>8000</v>
@@ -41355,7 +41355,7 @@
         <v>139</v>
       </c>
       <c r="AD425">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE425">
         <v>8000</v>
@@ -41450,7 +41450,7 @@
         <v>139</v>
       </c>
       <c r="AD426">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE426">
         <v>8000</v>
@@ -41545,7 +41545,7 @@
         <v>139</v>
       </c>
       <c r="AD427">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE427">
         <v>8000</v>
@@ -41640,7 +41640,7 @@
         <v>139</v>
       </c>
       <c r="AD428">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE428">
         <v>8000</v>
@@ -41735,7 +41735,7 @@
         <v>139</v>
       </c>
       <c r="AD429">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE429">
         <v>8000</v>
@@ -41830,7 +41830,7 @@
         <v>139</v>
       </c>
       <c r="AD430">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE430">
         <v>8000</v>
@@ -41925,7 +41925,7 @@
         <v>139</v>
       </c>
       <c r="AD431">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE431">
         <v>8000</v>
@@ -42023,7 +42023,7 @@
         <v>139</v>
       </c>
       <c r="AD432">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE432">
         <v>8000</v>
@@ -42121,7 +42121,7 @@
         <v>139</v>
       </c>
       <c r="AD433">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE433">
         <v>8000</v>
@@ -42219,7 +42219,7 @@
         <v>139</v>
       </c>
       <c r="AD434">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE434">
         <v>8000</v>
@@ -42314,7 +42314,7 @@
         <v>139</v>
       </c>
       <c r="AD435">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE435">
         <v>8000</v>
@@ -42409,7 +42409,7 @@
         <v>139</v>
       </c>
       <c r="AD436">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE436">
         <v>8000</v>
@@ -42504,7 +42504,7 @@
         <v>139</v>
       </c>
       <c r="AD437">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE437">
         <v>8000</v>
@@ -42599,7 +42599,7 @@
         <v>139</v>
       </c>
       <c r="AD438">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE438">
         <v>8000</v>
@@ -42694,7 +42694,7 @@
         <v>139</v>
       </c>
       <c r="AD439">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE439">
         <v>8000</v>
@@ -42789,7 +42789,7 @@
         <v>139</v>
       </c>
       <c r="AD440">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE440">
         <v>8000</v>
@@ -42884,7 +42884,7 @@
         <v>139</v>
       </c>
       <c r="AD441">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE441">
         <v>8000</v>
@@ -42979,7 +42979,7 @@
         <v>139</v>
       </c>
       <c r="AD442">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE442">
         <v>8000</v>
@@ -43074,7 +43074,7 @@
         <v>139</v>
       </c>
       <c r="AD443">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE443">
         <v>8000</v>
@@ -43169,7 +43169,7 @@
         <v>139</v>
       </c>
       <c r="AD444">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE444">
         <v>8000</v>
@@ -43264,7 +43264,7 @@
         <v>139</v>
       </c>
       <c r="AD445">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE445">
         <v>8000</v>
@@ -43359,7 +43359,7 @@
         <v>139</v>
       </c>
       <c r="AD446">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE446">
         <v>8000</v>
@@ -43454,7 +43454,7 @@
         <v>139</v>
       </c>
       <c r="AD447">
-        <v>10</v>
+        <v>14.47727272727272</v>
       </c>
       <c r="AE447">
         <v>8000</v>
@@ -43549,7 +43549,7 @@
         <v>139</v>
       </c>
       <c r="AD448">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE448">
         <v>8000</v>
@@ -43644,7 +43644,7 @@
         <v>139</v>
       </c>
       <c r="AD449">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE449">
         <v>8000</v>
@@ -43739,7 +43739,7 @@
         <v>139</v>
       </c>
       <c r="AD450">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE450">
         <v>8000</v>
@@ -43834,7 +43834,7 @@
         <v>139</v>
       </c>
       <c r="AD451">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE451">
         <v>8000</v>
@@ -43929,7 +43929,7 @@
         <v>139</v>
       </c>
       <c r="AD452">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE452">
         <v>8000</v>
@@ -44024,7 +44024,7 @@
         <v>139</v>
       </c>
       <c r="AD453">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE453">
         <v>8000</v>
@@ -44122,7 +44122,7 @@
         <v>139</v>
       </c>
       <c r="AD454">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE454">
         <v>8000</v>
@@ -44217,7 +44217,7 @@
         <v>139</v>
       </c>
       <c r="AD455">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE455">
         <v>8000</v>
@@ -44312,7 +44312,7 @@
         <v>139</v>
       </c>
       <c r="AD456">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE456">
         <v>8000</v>
@@ -44407,7 +44407,7 @@
         <v>139</v>
       </c>
       <c r="AD457">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE457">
         <v>8000</v>
@@ -44502,7 +44502,7 @@
         <v>139</v>
       </c>
       <c r="AD458">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE458">
         <v>8000</v>
@@ -44597,7 +44597,7 @@
         <v>139</v>
       </c>
       <c r="AD459">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE459">
         <v>8000</v>
@@ -44692,7 +44692,7 @@
         <v>139</v>
       </c>
       <c r="AD460">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE460">
         <v>8000</v>
@@ -44790,7 +44790,7 @@
         <v>139</v>
       </c>
       <c r="AD461">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE461">
         <v>8000</v>
@@ -46221,7 +46221,7 @@
         <v>139</v>
       </c>
       <c r="AD476">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE476">
         <v>8000</v>
@@ -46316,7 +46316,7 @@
         <v>139</v>
       </c>
       <c r="AD477">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE477">
         <v>8000</v>
@@ -46414,7 +46414,7 @@
         <v>139</v>
       </c>
       <c r="AD478">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE478">
         <v>8000</v>
@@ -46509,7 +46509,7 @@
         <v>139</v>
       </c>
       <c r="AD479">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE479">
         <v>8000</v>
@@ -46604,7 +46604,7 @@
         <v>139</v>
       </c>
       <c r="AD480">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE480">
         <v>8000</v>
@@ -46699,7 +46699,7 @@
         <v>139</v>
       </c>
       <c r="AD481">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE481">
         <v>8000</v>
@@ -46794,7 +46794,7 @@
         <v>139</v>
       </c>
       <c r="AD482">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE482">
         <v>8000</v>
@@ -46889,7 +46889,7 @@
         <v>139</v>
       </c>
       <c r="AD483">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE483">
         <v>8000</v>
@@ -46984,7 +46984,7 @@
         <v>139</v>
       </c>
       <c r="AD484">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE484">
         <v>8000</v>
@@ -47079,7 +47079,7 @@
         <v>139</v>
       </c>
       <c r="AD485">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE485">
         <v>8000</v>
@@ -47174,7 +47174,7 @@
         <v>139</v>
       </c>
       <c r="AD486">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE486">
         <v>8000</v>
@@ -47269,7 +47269,7 @@
         <v>139</v>
       </c>
       <c r="AD487">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE487">
         <v>8000</v>
@@ -47364,7 +47364,7 @@
         <v>139</v>
       </c>
       <c r="AD488">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE488">
         <v>8000</v>
@@ -47459,7 +47459,7 @@
         <v>139</v>
       </c>
       <c r="AD489">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE489">
         <v>8000</v>
@@ -47554,7 +47554,7 @@
         <v>139</v>
       </c>
       <c r="AD490">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE490">
         <v>8000</v>
@@ -47649,7 +47649,7 @@
         <v>139</v>
       </c>
       <c r="AD491">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE491">
         <v>8000</v>
@@ -47744,7 +47744,7 @@
         <v>139</v>
       </c>
       <c r="AD492">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE492">
         <v>8000</v>
@@ -47842,7 +47842,7 @@
         <v>139</v>
       </c>
       <c r="AD493">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE493">
         <v>8000</v>
@@ -47940,7 +47940,7 @@
         <v>139</v>
       </c>
       <c r="AD494">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE494">
         <v>8000</v>
@@ -48035,7 +48035,7 @@
         <v>139</v>
       </c>
       <c r="AD495">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE495">
         <v>8000</v>
@@ -48130,7 +48130,7 @@
         <v>139</v>
       </c>
       <c r="AD496">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE496">
         <v>8000</v>
